--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3851,6 +3851,112 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128533174</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grötholen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>372182</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6860436</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92746</v>
+        <v>92752</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92752</v>
+        <v>92758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2023 artfynd.xlsx
+++ b/artfynd/A 28823-2023 artfynd.xlsx
@@ -3856,7 +3856,7 @@
         <v>128533174</v>
       </c>
       <c r="B27" t="n">
-        <v>92815</v>
+        <v>92823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
